--- a/outputs/280-17.xlsx
+++ b/outputs/280-17.xlsx
@@ -116,12 +116,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -374,60 +378,48 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="n">
+      <c r="B1" s="2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="2" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="2" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="2" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="1"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="1"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="1"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="1"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/outputs/280-17.xlsx
+++ b/outputs/280-17.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="8">
   <si>
     <t xml:space="preserve">DATA 3</t>
   </si>
@@ -35,6 +35,15 @@
   </si>
   <si>
     <t xml:space="preserve">DATA 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DATA 7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DATA 8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DATA 11</t>
   </si>
 </sst>
 </file>
@@ -378,14 +387,14 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="n">
+      <c r="B1" s="1" t="n">
         <v>1</v>
       </c>
     </row>
@@ -393,7 +402,7 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B2" s="1" t="n">
         <v>2</v>
       </c>
     </row>
@@ -409,7 +418,7 @@
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B4" s="1" t="n">
         <v>4</v>
       </c>
     </row>
@@ -417,7 +426,63 @@
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="B5" s="1" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="2" t="n">
         <v>5</v>
       </c>
     </row>
